--- a/output/第10期計画_将来推計_人口と認定者数.xlsx
+++ b/output/第10期計画_将来推計_人口と認定者数.xlsx
@@ -644,7 +644,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>人口推計の基礎について社人研推計（見える化システムの初期値）をそのまま用いることが決定した（令和8年7月30日）。これを受けて将来推計の第1段階（人口と認定者数）を行う。第2段階（サービス見込量）以降は、サービス種別ごとの利用率と単価を要するため、資料の受領及び方針の決定を待つ。作成日：令和8年7月30日。</t>
+          <t>人口推計の基礎について社人研推計（見える化システムの初期値）をそのまま用いることを受託者の案とし、これを仮に置いて将来推計の第1段階（人口と認定者数）を試算する。人口推計の基礎の採用は発注者のご意向による。第2段階（サービス見込量）以降は、サービス種別ごとの利用率と単価を要するため、資料の受領及び方針の決定を待つ。作成日：令和8年7月30日。</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>決定した人口推計の基礎を確認する。</t>
+          <t>試算の前提とした人口推計の基礎を確認する。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>方針No.1 決定済</t>
+          <t>方針No.1 確認待ち</t>
         </is>
       </c>
     </row>
@@ -1136,14 +1136,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>人口推計の基礎（決定：社人研推計をそのまま用いる）</t>
+          <t>人口推計の基礎（受託者の案：社人研推計をそのまま用いる）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和8年7月30日、人口推計の基礎について社人研推計（見える化システムの初期値）をそのまま用いることが決定した。見える化A系列の値をそのまま前提とする。</t>
+          <t>令和8年7月30日、人口推計の基礎について社人研推計（見える化システムの初期値）をそのまま用いることを受託者の案とする。見える化A系列の値をそのまま前提とする。</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>【決定の記録】</t>
+          <t>【推計の前提の記録】</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>決定事項</t>
+          <t>試算の前提（受託者の案）</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1572,12 +1572,12 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>決定日</t>
+          <t>この前提の位置付け</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>令和8年7月30日</t>
+          <t>受託者の案であり、決定した事項ではない。仕様書の定めにより、業務の各工程においてその都度発注者の意向を確認する。本シートの試算は、作業を止めないためにこの案を仮に置いたものである。</t>
         </is>
       </c>
       <c r="C19" s="24" t="n"/>
@@ -1591,12 +1591,12 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>決定の内容</t>
+          <t>意向を確認する時期</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>広域連合からの意向がない場合は見える化システムの値により進める。</t>
+          <t>キックオフ会議（ヒアリングシート項目6-1）。他の系列によるとの意向がある場合は、02〜06シートを再計算する。</t>
         </is>
       </c>
       <c r="C20" s="24" t="n"/>
@@ -1610,7 +1610,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>選ばなかった選択肢</t>
+          <t>仮に置かなかった選択肢</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>この決定を記録する理由</t>
+          <t>この前提を記録する理由</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>第2章第1節に、人口推計の基礎を社人研推計とすること、第9期計画（住民基本台帳・コーホート変化率法）の数値と一致しないこと、及びその理由を記載する。</t>
+          <t>意向の確認を経て基礎が定まった段階で、第2章第1節に、人口推計の基礎、第9期計画（住民基本台帳・コーホート変化率法）の数値と一致しないこと、及びその理由を記載する。現時点の計画素案では当該箇所に［要協議］を付している。</t>
         </is>
       </c>
       <c r="C23" s="24" t="n"/>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳実績（資料No.9）を受領した際は、社人研推計との乖離を確認し、乖離が大きい場合は第2章に注記する。推計の基礎そのものは変更しない。</t>
+          <t>令和6年・令和7年の町別住民基本台帳実績（資料No.9）を受領した際は、社人研推計との乖離を確認し、社人研推計との乖離を確認し、乖離が大きい場合は第2章に注記する。基礎そのものを変更するかどうかは発注者の意向による。</t>
         </is>
       </c>
       <c r="C24" s="24" t="n"/>

--- a/output/第10期計画_将来推計_人口と認定者数.xlsx
+++ b/output/第10期計画_将来推計_人口と認定者数.xlsx
@@ -644,7 +644,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>人口推計の基礎について社人研推計（見える化システムの初期値）をそのまま用いることを受託者の案とし、これを仮に置いて将来推計の第1段階（人口と認定者数）を試算する。人口推計の基礎の採用は発注者のご意向による。第2段階（サービス見込量）以降は、サービス種別ごとの利用率と単価を要するため、資料の受領及び方針の決定を待つ。作成日：令和8年7月30日。</t>
+          <t>人口推計の基礎について社人研推計（見える化システムの初期値）をそのまま用いることを受託者の案とし、これを仮に置いて将来推計の第1段階（人口と認定者数）を試算する。人口推計の基礎の採用は発注者のご意向による。第2段階（サービス見込量）は、令和8年8月4日に受領した見える化B3系列・D系列により別冊「将来推計 第2段階　サービス見込量」（8シート）として試算した。第3段階（給付費・保険料）は単価を要するため、資料の受領及び方針の決定を待つ。作成日：令和8年7月30日（第2段階の追記：令和8年8月4日）。</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4435,17 +4435,17 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>要介護度別認定者数の実績（令和元年〜令和8年度）</t>
+          <t>要介護度別認定者数の実績（令和元年〜令和8年度）【令和8年8月4日受領済】</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>要支援1・2、要介護1〜5の別。各年3月末。見える化B系列又は保険者の統計による。</t>
+          <t>要支援1・2、要介護1〜5の別。各年3月末。見える化B3-a系列により平成19年3月末〜令和8年3月末の20時点を入手した。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>要介護度別の認定者数を推計できない。サービス見込量は要介護度別の利用率により算定するため、第2段階に進めない。</t>
+          <t>（解消済み）要介護度別の構成比を令和8年3月末の実績で固定して第2段階を試算した。</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>受領済</t>
         </is>
       </c>
     </row>
@@ -4470,17 +4470,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>サービス種別・要介護度別の利用率と受給者数（令和4〜7年度）</t>
+          <t>サービス種別・要介護度別の利用率と受給者数（令和4〜7年度）【令和8年8月4日受領済】</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>認定者のうち各サービスを利用した者の割合と実人数。見える化D系列又は国保連の給付実績情報による。</t>
+          <t>認定者のうち各サービスを利用した者の割合と実人数。見える化D45・D46系列により入手した。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>サービス見込量を算定できない。</t>
+          <t>（解消済み）令和7年度の利用率により第2段階を試算した。残るのは居住系・施設の種別別受給者数と総合事業の実績である。</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>受領済</t>
         </is>
       </c>
     </row>
@@ -4834,24 +4834,24 @@
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>要介護度別認定者数の受領と第1段階の確定</t>
+          <t>要介護度別認定者数・利用率の受領と第2段階の試算</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>上表No.2</t>
+          <t>上表No.2・No.3（実施済）</t>
         </is>
       </c>
       <c r="D20" s="24" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>認定者数の見込み（要介護度別）</t>
+          <t>将来推計 第2段階（サービス見込量）</t>
         </is>
       </c>
       <c r="G20" s="8" t="n"/>
@@ -4859,24 +4859,24 @@
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>第2段階（サービス見込量）の算定</t>
+          <t>認定率のシナリオの決定による第1段階の確定</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>上表No.1・No.3〜No.7</t>
+          <t>上表No.1</t>
         </is>
       </c>
       <c r="D21" s="24" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>サービス見込量推計表</t>
+          <t>認定者数の見込み（要介護度別）</t>
         </is>
       </c>
       <c r="G21" s="8" t="n"/>
@@ -4884,24 +4884,24 @@
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>第3段階（給付費・保険料）の算定</t>
+          <t>第2段階の確定（施策効果・供給制約の反映）</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>上表No.8〜No.10</t>
+          <t>上表No.1・No.4〜No.7</t>
         </is>
       </c>
       <c r="D22" s="24" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>給付費見込表・保険料算定表</t>
+          <t>サービス見込量推計表</t>
         </is>
       </c>
       <c r="G22" s="8" t="n"/>
@@ -4909,24 +4909,24 @@
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>計画素案の第6章への反映</t>
+          <t>第3段階（給付費・保険料）の算定</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>上記すべて</t>
+          <t>上表No.8〜No.10</t>
         </is>
       </c>
       <c r="D23" s="24" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>計画素案（確定版）</t>
+          <t>給付費見込表・保険料算定表</t>
         </is>
       </c>
       <c r="G23" s="8" t="n"/>
@@ -4934,51 +4934,78 @@
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>R9.1〜2</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>告示を受けた最終確定</t>
+          <t>計画素案の第6章への反映</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>上表No.11</t>
+          <t>上記すべて</t>
         </is>
       </c>
       <c r="D24" s="24" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
+          <t>計画素案（確定版）</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>R9.1〜2</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>告示を受けた最終確定</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>上表No.11</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>計画最終案</t>
         </is>
       </c>
-      <c r="G24" s="8" t="n"/>
-    </row>
-    <row r="26" ht="104" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>注1）第1段階（本表）は、認定率のシナリオの決定（No.1）と要介護度別認定者数の受領（No.2）により確定する。この2つが令和8年9月中に整えば、第2段階を令和8年10月に行い、令和8年12月の工程に間に合う。注2）No.2（要介護度別認定者数）は新規の資料依頼である。サービス見込量は要介護度別の利用率により算定するため、これがないと第2段階に進めない。必要事項の一覧01シートに追加する。注3）第3段階（保険料）は国の告示を待つ部分があるため、令和9年1月から2月に最終確定となる。この期間は作業が集中するため、それまでに確定できる部分（見込量・給付費の構造）を令和8年12月までに終えておく。</t>
+      <c r="G25" s="8" t="n"/>
+    </row>
+    <row r="27" ht="104" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>注1）No.2（要介護度別認定者数）とNo.3（利用率・受給者数）は令和8年8月4日に見える化B3系列・D系列として受領し、解消した。これにより第2段階（サービス見込量）を先行して試算し、別冊「将来推計 第2段階　サービス見込量」（8シート）として取りまとめた。第1段階（本表）は、残る認定率のシナリオの決定（No.1）により確定する。これが令和8年9月中に整えば、第2段階の確定を令和8年10月に行い、令和8年12月の工程に間に合う。注3）第3段階（保険料）は国の告示を待つ部分があるため、令和9年1月から2月に最終確定となる。この期間は作業が集中するため、それまでに確定できる部分（見込量・給付費の構造）を令和8年12月までに終えておく。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="C19:E19"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="F25:G25"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C25:E25"/>
     <mergeCell ref="C24:E24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_将来推計_人口と認定者数.xlsx
+++ b/output/第10期計画_将来推計_人口と認定者数.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_第9期の推計との対比" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_推計の限界と感度" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_第2段階以降に必要な決定と資料" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_計算過程確認（再計算可能）" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -181,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -258,6 +262,27 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5010,4 +5035,2092 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>計算過程確認シート（入力値を変えると出力が更新される）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>他のシートは算定結果を書き出した転記表であるが、本シートはセルに計算式を入れている。黄色の入力欄（設定・階級別の基準値・社人研推計の階級別人口）を変更すると、階級別人口・認定率・認定者数・計画本文への転記値がすべて更新される。第三者による検算及び、修正値を受領したときの更新に用いる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>【1　入力欄①　推計の設定】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>基準年度（西暦）</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="24" t="n"/>
+      <c r="G6" s="24" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>階級別人口・認定率の基準となる年。令和7年度＝2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>シナリオ</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="24" t="n"/>
+      <c r="G7" s="24" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>1＝現状固定／2＝トレンド継続／3＝令和元年水準へ回帰。計画本文は2による</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>トレンドの延長年数</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="24" t="n"/>
+      <c r="G8" s="24" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>基準年度から何年まで認定率の変化を延長するか。以後は固定</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>人口補正の適用</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="24" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>0＝適用しない／1＝適用する。1にすると【2】の補正係数が階級別人口に乗じられる</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>【2　入力欄②　階級別の基準値】</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>階級</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>基準人口
+（令和8年3月末）</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>基準認定率
+（％）</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>令和元年
+認定率（％）</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>補正係数</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>年平均変化
+（pt・計算値）</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>65〜74歳</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="29">
+        <f>(C13-D13)/7</f>
+        <v/>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>補正係数は人口推計の補正（案B）による。65〜74歳1.0377／75歳以上0.9927</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>75〜84歳</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>3499</v>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="29">
+        <f>(C14-D14)/7</f>
+        <v/>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>補正係数は人口推計の補正（案B）による。65〜74歳1.0377／75歳以上0.9927</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>85歳以上</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>63</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="29">
+        <f>(C15-D15)/7</f>
+        <v/>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>補正係数は人口推計の補正（案B）による。65〜74歳1.0377／75歳以上0.9927</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>【3　入力欄③　社人研推計の階級別人口（見える化A4）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>西暦</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>65〜74歳</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>75〜84歳</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>85歳以上</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>3622</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>3534</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>2167</v>
+      </c>
+      <c r="F19" s="9">
+        <f>SUM(C19:E19)</f>
+        <v/>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>基準</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>3572</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>3559</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>2190</v>
+      </c>
+      <c r="F20" s="9">
+        <f>SUM(C20:E20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>3522</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>3583</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>2212</v>
+      </c>
+      <c r="F21" s="9">
+        <f>SUM(C21:E21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>第10期</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>3473</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>3609</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>2234</v>
+      </c>
+      <c r="F22" s="9">
+        <f>SUM(C22:E22)</f>
+        <v/>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>第10期</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>2029</v>
+      </c>
+      <c r="C23" s="19" t="n">
+        <v>3423</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>3633</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>2256</v>
+      </c>
+      <c r="F23" s="9">
+        <f>SUM(C23:E23)</f>
+        <v/>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>第10期</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>3373</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>3658</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>2279</v>
+      </c>
+      <c r="F24" s="9">
+        <f>SUM(C24:E24)</f>
+        <v/>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>3585</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>3120</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>2673</v>
+      </c>
+      <c r="F25" s="9">
+        <f>SUM(C25:E25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>中長期</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>3885</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>2938</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F26" s="9">
+        <f>SUM(C26:E26)</f>
+        <v/>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>中長期</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>3776</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>3150</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>2596</v>
+      </c>
+      <c r="F27" s="9">
+        <f>SUM(C27:E27)</f>
+        <v/>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>中長期</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>3261</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>3444</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>2534</v>
+      </c>
+      <c r="F28" s="9">
+        <f>SUM(C28:E28)</f>
+        <v/>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>中長期</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>【4　計算欄　推計上の階級別人口　＝　基準人口×社人研の伸び率×補正係数】</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>西暦</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>65〜74歳</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>75〜84歳</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>85歳以上</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>65歳以上</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>計算式</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C32" s="30">
+        <f>$B$13*C19/C$19*IF($B$9=1,$E$13,1)</f>
+        <v/>
+      </c>
+      <c r="D32" s="30">
+        <f>$B$14*D19/D$19*IF($B$9=1,$E$14,1)</f>
+        <v/>
+      </c>
+      <c r="E32" s="30">
+        <f>$B$15*E19/E$19*IF($B$9=1,$E$15,1)</f>
+        <v/>
+      </c>
+      <c r="F32" s="30">
+        <f>SUM(C32:E32)</f>
+        <v/>
+      </c>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>基準人口×当年の社人研人口÷基準年の社人研人口×補正係数（適用する場合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C33" s="30">
+        <f>$B$13*C20/C$19*IF($B$9=1,$E$13,1)</f>
+        <v/>
+      </c>
+      <c r="D33" s="30">
+        <f>$B$14*D20/D$19*IF($B$9=1,$E$14,1)</f>
+        <v/>
+      </c>
+      <c r="E33" s="30">
+        <f>$B$15*E20/E$19*IF($B$9=1,$E$15,1)</f>
+        <v/>
+      </c>
+      <c r="F33" s="30">
+        <f>SUM(C33:E33)</f>
+        <v/>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C34" s="30">
+        <f>$B$13*C21/C$19*IF($B$9=1,$E$13,1)</f>
+        <v/>
+      </c>
+      <c r="D34" s="30">
+        <f>$B$14*D21/D$19*IF($B$9=1,$E$14,1)</f>
+        <v/>
+      </c>
+      <c r="E34" s="30">
+        <f>$B$15*E21/E$19*IF($B$9=1,$E$15,1)</f>
+        <v/>
+      </c>
+      <c r="F34" s="30">
+        <f>SUM(C34:E34)</f>
+        <v/>
+      </c>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C35" s="30">
+        <f>$B$13*C22/C$19*IF($B$9=1,$E$13,1)</f>
+        <v/>
+      </c>
+      <c r="D35" s="30">
+        <f>$B$14*D22/D$19*IF($B$9=1,$E$14,1)</f>
+        <v/>
+      </c>
+      <c r="E35" s="30">
+        <f>$B$15*E22/E$19*IF($B$9=1,$E$15,1)</f>
+        <v/>
+      </c>
+      <c r="F35" s="30">
+        <f>SUM(C35:E35)</f>
+        <v/>
+      </c>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>2029</v>
+      </c>
+      <c r="C36" s="30">
+        <f>$B$13*C23/C$19*IF($B$9=1,$E$13,1)</f>
+        <v/>
+      </c>
+      <c r="D36" s="30">
+        <f>$B$14*D23/D$19*IF($B$9=1,$E$14,1)</f>
+        <v/>
+      </c>
+      <c r="E36" s="30">
+        <f>$B$15*E23/E$19*IF($B$9=1,$E$15,1)</f>
+        <v/>
+      </c>
+      <c r="F36" s="30">
+        <f>SUM(C36:E36)</f>
+        <v/>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C37" s="30">
+        <f>$B$13*C24/C$19*IF($B$9=1,$E$13,1)</f>
+        <v/>
+      </c>
+      <c r="D37" s="30">
+        <f>$B$14*D24/D$19*IF($B$9=1,$E$14,1)</f>
+        <v/>
+      </c>
+      <c r="E37" s="30">
+        <f>$B$15*E24/E$19*IF($B$9=1,$E$15,1)</f>
+        <v/>
+      </c>
+      <c r="F37" s="30">
+        <f>SUM(C37:E37)</f>
+        <v/>
+      </c>
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C38" s="30">
+        <f>$B$13*C25/C$19*IF($B$9=1,$E$13,1)</f>
+        <v/>
+      </c>
+      <c r="D38" s="30">
+        <f>$B$14*D25/D$19*IF($B$9=1,$E$14,1)</f>
+        <v/>
+      </c>
+      <c r="E38" s="30">
+        <f>$B$15*E25/E$19*IF($B$9=1,$E$15,1)</f>
+        <v/>
+      </c>
+      <c r="F38" s="30">
+        <f>SUM(C38:E38)</f>
+        <v/>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C39" s="30">
+        <f>$B$13*C26/C$19*IF($B$9=1,$E$13,1)</f>
+        <v/>
+      </c>
+      <c r="D39" s="30">
+        <f>$B$14*D26/D$19*IF($B$9=1,$E$14,1)</f>
+        <v/>
+      </c>
+      <c r="E39" s="30">
+        <f>$B$15*E26/E$19*IF($B$9=1,$E$15,1)</f>
+        <v/>
+      </c>
+      <c r="F39" s="30">
+        <f>SUM(C39:E39)</f>
+        <v/>
+      </c>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C40" s="30">
+        <f>$B$13*C27/C$19*IF($B$9=1,$E$13,1)</f>
+        <v/>
+      </c>
+      <c r="D40" s="30">
+        <f>$B$14*D27/D$19*IF($B$9=1,$E$14,1)</f>
+        <v/>
+      </c>
+      <c r="E40" s="30">
+        <f>$B$15*E27/E$19*IF($B$9=1,$E$15,1)</f>
+        <v/>
+      </c>
+      <c r="F40" s="30">
+        <f>SUM(C40:E40)</f>
+        <v/>
+      </c>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" s="30">
+        <f>$B$13*C28/C$19*IF($B$9=1,$E$13,1)</f>
+        <v/>
+      </c>
+      <c r="D41" s="30">
+        <f>$B$14*D28/D$19*IF($B$9=1,$E$14,1)</f>
+        <v/>
+      </c>
+      <c r="E41" s="30">
+        <f>$B$15*E28/E$19*IF($B$9=1,$E$15,1)</f>
+        <v/>
+      </c>
+      <c r="F41" s="30">
+        <f>SUM(C41:E41)</f>
+        <v/>
+      </c>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="5" t="inlineStr"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>【5　計算欄　階級別認定率（シナリオにより切り替わる）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>西暦</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>65〜74歳</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>75〜84歳</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>85歳以上</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>計算式</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C45" s="31">
+        <f>CHOOSE($B$7,$C$13,$C$13+$F$13*MIN(MAX(B45-$B$6,0),$B$8),$C$13+($D$13-$C$13)*MIN(MAX(B45-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D45" s="31">
+        <f>CHOOSE($B$7,$C$14,$C$14+$F$14*MIN(MAX(B45-$B$6,0),$B$8),$C$14+($D$14-$C$14)*MIN(MAX(B45-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="E45" s="31">
+        <f>CHOOSE($B$7,$C$15,$C$15+$F$15*MIN(MAX(B45-$B$6,0),$B$8),$C$15+($D$15-$C$15)*MIN(MAX(B45-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="24" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>CHOOSE(シナリオ，基準率，基準率＋年平均変化×経過年数，基準率＋（令和元年率－基準率）×経過年数÷延長年数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C46" s="31">
+        <f>CHOOSE($B$7,$C$13,$C$13+$F$13*MIN(MAX(B46-$B$6,0),$B$8),$C$13+($D$13-$C$13)*MIN(MAX(B46-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D46" s="31">
+        <f>CHOOSE($B$7,$C$14,$C$14+$F$14*MIN(MAX(B46-$B$6,0),$B$8),$C$14+($D$14-$C$14)*MIN(MAX(B46-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="E46" s="31">
+        <f>CHOOSE($B$7,$C$15,$C$15+$F$15*MIN(MAX(B46-$B$6,0),$B$8),$C$15+($D$15-$C$15)*MIN(MAX(B46-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="24" t="n"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C47" s="31">
+        <f>CHOOSE($B$7,$C$13,$C$13+$F$13*MIN(MAX(B47-$B$6,0),$B$8),$C$13+($D$13-$C$13)*MIN(MAX(B47-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D47" s="31">
+        <f>CHOOSE($B$7,$C$14,$C$14+$F$14*MIN(MAX(B47-$B$6,0),$B$8),$C$14+($D$14-$C$14)*MIN(MAX(B47-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="E47" s="31">
+        <f>CHOOSE($B$7,$C$15,$C$15+$F$15*MIN(MAX(B47-$B$6,0),$B$8),$C$15+($D$15-$C$15)*MIN(MAX(B47-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="24" t="n"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C48" s="31">
+        <f>CHOOSE($B$7,$C$13,$C$13+$F$13*MIN(MAX(B48-$B$6,0),$B$8),$C$13+($D$13-$C$13)*MIN(MAX(B48-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D48" s="31">
+        <f>CHOOSE($B$7,$C$14,$C$14+$F$14*MIN(MAX(B48-$B$6,0),$B$8),$C$14+($D$14-$C$14)*MIN(MAX(B48-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="E48" s="31">
+        <f>CHOOSE($B$7,$C$15,$C$15+$F$15*MIN(MAX(B48-$B$6,0),$B$8),$C$15+($D$15-$C$15)*MIN(MAX(B48-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="24" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>2029</v>
+      </c>
+      <c r="C49" s="31">
+        <f>CHOOSE($B$7,$C$13,$C$13+$F$13*MIN(MAX(B49-$B$6,0),$B$8),$C$13+($D$13-$C$13)*MIN(MAX(B49-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D49" s="31">
+        <f>CHOOSE($B$7,$C$14,$C$14+$F$14*MIN(MAX(B49-$B$6,0),$B$8),$C$14+($D$14-$C$14)*MIN(MAX(B49-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="E49" s="31">
+        <f>CHOOSE($B$7,$C$15,$C$15+$F$15*MIN(MAX(B49-$B$6,0),$B$8),$C$15+($D$15-$C$15)*MIN(MAX(B49-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="24" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C50" s="31">
+        <f>CHOOSE($B$7,$C$13,$C$13+$F$13*MIN(MAX(B50-$B$6,0),$B$8),$C$13+($D$13-$C$13)*MIN(MAX(B50-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D50" s="31">
+        <f>CHOOSE($B$7,$C$14,$C$14+$F$14*MIN(MAX(B50-$B$6,0),$B$8),$C$14+($D$14-$C$14)*MIN(MAX(B50-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="E50" s="31">
+        <f>CHOOSE($B$7,$C$15,$C$15+$F$15*MIN(MAX(B50-$B$6,0),$B$8),$C$15+($D$15-$C$15)*MIN(MAX(B50-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="24" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C51" s="31">
+        <f>CHOOSE($B$7,$C$13,$C$13+$F$13*MIN(MAX(B51-$B$6,0),$B$8),$C$13+($D$13-$C$13)*MIN(MAX(B51-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D51" s="31">
+        <f>CHOOSE($B$7,$C$14,$C$14+$F$14*MIN(MAX(B51-$B$6,0),$B$8),$C$14+($D$14-$C$14)*MIN(MAX(B51-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="E51" s="31">
+        <f>CHOOSE($B$7,$C$15,$C$15+$F$15*MIN(MAX(B51-$B$6,0),$B$8),$C$15+($D$15-$C$15)*MIN(MAX(B51-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="24" t="n"/>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C52" s="31">
+        <f>CHOOSE($B$7,$C$13,$C$13+$F$13*MIN(MAX(B52-$B$6,0),$B$8),$C$13+($D$13-$C$13)*MIN(MAX(B52-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D52" s="31">
+        <f>CHOOSE($B$7,$C$14,$C$14+$F$14*MIN(MAX(B52-$B$6,0),$B$8),$C$14+($D$14-$C$14)*MIN(MAX(B52-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="E52" s="31">
+        <f>CHOOSE($B$7,$C$15,$C$15+$F$15*MIN(MAX(B52-$B$6,0),$B$8),$C$15+($D$15-$C$15)*MIN(MAX(B52-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="24" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C53" s="31">
+        <f>CHOOSE($B$7,$C$13,$C$13+$F$13*MIN(MAX(B53-$B$6,0),$B$8),$C$13+($D$13-$C$13)*MIN(MAX(B53-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D53" s="31">
+        <f>CHOOSE($B$7,$C$14,$C$14+$F$14*MIN(MAX(B53-$B$6,0),$B$8),$C$14+($D$14-$C$14)*MIN(MAX(B53-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="E53" s="31">
+        <f>CHOOSE($B$7,$C$15,$C$15+$F$15*MIN(MAX(B53-$B$6,0),$B$8),$C$15+($D$15-$C$15)*MIN(MAX(B53-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="24" t="n"/>
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C54" s="31">
+        <f>CHOOSE($B$7,$C$13,$C$13+$F$13*MIN(MAX(B54-$B$6,0),$B$8),$C$13+($D$13-$C$13)*MIN(MAX(B54-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D54" s="31">
+        <f>CHOOSE($B$7,$C$14,$C$14+$F$14*MIN(MAX(B54-$B$6,0),$B$8),$C$14+($D$14-$C$14)*MIN(MAX(B54-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="E54" s="31">
+        <f>CHOOSE($B$7,$C$15,$C$15+$F$15*MIN(MAX(B54-$B$6,0),$B$8),$C$15+($D$15-$C$15)*MIN(MAX(B54-$B$6,0),$B$8)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="24" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>【6　計算欄　認定者数　＝　階級別人口×階級別認定率÷100】</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>西暦</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>65〜74歳</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>75〜84歳</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>85歳以上</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>認定者数計</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>認定率（％）</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C58" s="30">
+        <f>C32*C45/100</f>
+        <v/>
+      </c>
+      <c r="D58" s="30">
+        <f>D32*D45/100</f>
+        <v/>
+      </c>
+      <c r="E58" s="30">
+        <f>E32*E45/100</f>
+        <v/>
+      </c>
+      <c r="F58" s="32">
+        <f>SUM(C58:E58)</f>
+        <v/>
+      </c>
+      <c r="G58" s="33">
+        <f>F58/F32*100</f>
+        <v/>
+      </c>
+      <c r="H58" s="5" t="inlineStr"/>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>基準</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C59" s="30">
+        <f>C33*C46/100</f>
+        <v/>
+      </c>
+      <c r="D59" s="30">
+        <f>D33*D46/100</f>
+        <v/>
+      </c>
+      <c r="E59" s="30">
+        <f>E33*E46/100</f>
+        <v/>
+      </c>
+      <c r="F59" s="32">
+        <f>SUM(C59:E59)</f>
+        <v/>
+      </c>
+      <c r="G59" s="33">
+        <f>F59/F33*100</f>
+        <v/>
+      </c>
+      <c r="H59" s="5" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C60" s="30">
+        <f>C34*C47/100</f>
+        <v/>
+      </c>
+      <c r="D60" s="30">
+        <f>D34*D47/100</f>
+        <v/>
+      </c>
+      <c r="E60" s="30">
+        <f>E34*E47/100</f>
+        <v/>
+      </c>
+      <c r="F60" s="32">
+        <f>SUM(C60:E60)</f>
+        <v/>
+      </c>
+      <c r="G60" s="33">
+        <f>F60/F34*100</f>
+        <v/>
+      </c>
+      <c r="H60" s="5" t="inlineStr"/>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>第10期</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C61" s="30">
+        <f>C35*C48/100</f>
+        <v/>
+      </c>
+      <c r="D61" s="30">
+        <f>D35*D48/100</f>
+        <v/>
+      </c>
+      <c r="E61" s="30">
+        <f>E35*E48/100</f>
+        <v/>
+      </c>
+      <c r="F61" s="32">
+        <f>SUM(C61:E61)</f>
+        <v/>
+      </c>
+      <c r="G61" s="33">
+        <f>F61/F35*100</f>
+        <v/>
+      </c>
+      <c r="H61" s="5" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>第10期</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>2029</v>
+      </c>
+      <c r="C62" s="30">
+        <f>C36*C49/100</f>
+        <v/>
+      </c>
+      <c r="D62" s="30">
+        <f>D36*D49/100</f>
+        <v/>
+      </c>
+      <c r="E62" s="30">
+        <f>E36*E49/100</f>
+        <v/>
+      </c>
+      <c r="F62" s="32">
+        <f>SUM(C62:E62)</f>
+        <v/>
+      </c>
+      <c r="G62" s="33">
+        <f>F62/F36*100</f>
+        <v/>
+      </c>
+      <c r="H62" s="5" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>第10期</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C63" s="30">
+        <f>C37*C50/100</f>
+        <v/>
+      </c>
+      <c r="D63" s="30">
+        <f>D37*D50/100</f>
+        <v/>
+      </c>
+      <c r="E63" s="30">
+        <f>E37*E50/100</f>
+        <v/>
+      </c>
+      <c r="F63" s="32">
+        <f>SUM(C63:E63)</f>
+        <v/>
+      </c>
+      <c r="G63" s="33">
+        <f>F63/F37*100</f>
+        <v/>
+      </c>
+      <c r="H63" s="5" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C64" s="30">
+        <f>C38*C51/100</f>
+        <v/>
+      </c>
+      <c r="D64" s="30">
+        <f>D38*D51/100</f>
+        <v/>
+      </c>
+      <c r="E64" s="30">
+        <f>E38*E51/100</f>
+        <v/>
+      </c>
+      <c r="F64" s="32">
+        <f>SUM(C64:E64)</f>
+        <v/>
+      </c>
+      <c r="G64" s="33">
+        <f>F64/F38*100</f>
+        <v/>
+      </c>
+      <c r="H64" s="5" t="inlineStr"/>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>中長期</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C65" s="30">
+        <f>C39*C52/100</f>
+        <v/>
+      </c>
+      <c r="D65" s="30">
+        <f>D39*D52/100</f>
+        <v/>
+      </c>
+      <c r="E65" s="30">
+        <f>E39*E52/100</f>
+        <v/>
+      </c>
+      <c r="F65" s="32">
+        <f>SUM(C65:E65)</f>
+        <v/>
+      </c>
+      <c r="G65" s="33">
+        <f>F65/F39*100</f>
+        <v/>
+      </c>
+      <c r="H65" s="5" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>中長期</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C66" s="30">
+        <f>C40*C53/100</f>
+        <v/>
+      </c>
+      <c r="D66" s="30">
+        <f>D40*D53/100</f>
+        <v/>
+      </c>
+      <c r="E66" s="30">
+        <f>E40*E53/100</f>
+        <v/>
+      </c>
+      <c r="F66" s="32">
+        <f>SUM(C66:E66)</f>
+        <v/>
+      </c>
+      <c r="G66" s="33">
+        <f>F66/F40*100</f>
+        <v/>
+      </c>
+      <c r="H66" s="5" t="inlineStr"/>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>中長期</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C67" s="30">
+        <f>C41*C54/100</f>
+        <v/>
+      </c>
+      <c r="D67" s="30">
+        <f>D41*D54/100</f>
+        <v/>
+      </c>
+      <c r="E67" s="30">
+        <f>E41*E54/100</f>
+        <v/>
+      </c>
+      <c r="F67" s="32">
+        <f>SUM(C67:E67)</f>
+        <v/>
+      </c>
+      <c r="G67" s="33">
+        <f>F67/F41*100</f>
+        <v/>
+      </c>
+      <c r="H67" s="5" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>中長期</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>【7　出力　計画本文への転記値】</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr"/>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr"/>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>転記先</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="34" t="inlineStr">
+        <is>
+          <t>令和9年度の認定者数</t>
+        </is>
+      </c>
+      <c r="B71" s="35">
+        <f>ROUND(F60,0)</f>
+        <v/>
+      </c>
+      <c r="C71" s="24" t="n"/>
+      <c r="D71" s="24" t="n"/>
+      <c r="E71" s="24" t="n"/>
+      <c r="F71" s="24" t="n"/>
+      <c r="G71" s="24" t="n"/>
+      <c r="H71" s="8" t="n"/>
+      <c r="I71" s="34" t="inlineStr">
+        <is>
+          <t>第6章第1節</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="34" t="inlineStr">
+        <is>
+          <t>令和10年度の認定者数</t>
+        </is>
+      </c>
+      <c r="B72" s="35">
+        <f>ROUND(F61,0)</f>
+        <v/>
+      </c>
+      <c r="C72" s="24" t="n"/>
+      <c r="D72" s="24" t="n"/>
+      <c r="E72" s="24" t="n"/>
+      <c r="F72" s="24" t="n"/>
+      <c r="G72" s="24" t="n"/>
+      <c r="H72" s="8" t="n"/>
+      <c r="I72" s="34" t="inlineStr">
+        <is>
+          <t>第6章第1節</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="34" t="inlineStr">
+        <is>
+          <t>令和11年度の認定者数</t>
+        </is>
+      </c>
+      <c r="B73" s="35">
+        <f>ROUND(F62,0)</f>
+        <v/>
+      </c>
+      <c r="C73" s="24" t="n"/>
+      <c r="D73" s="24" t="n"/>
+      <c r="E73" s="24" t="n"/>
+      <c r="F73" s="24" t="n"/>
+      <c r="G73" s="24" t="n"/>
+      <c r="H73" s="8" t="n"/>
+      <c r="I73" s="34" t="inlineStr">
+        <is>
+          <t>第6章第1節</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="34" t="inlineStr">
+        <is>
+          <t>第10期3年計</t>
+        </is>
+      </c>
+      <c r="B74" s="35">
+        <f>ROUND(F60,0)+ROUND(F61,0)+ROUND(F62,0)</f>
+        <v/>
+      </c>
+      <c r="C74" s="24" t="n"/>
+      <c r="D74" s="24" t="n"/>
+      <c r="E74" s="24" t="n"/>
+      <c r="F74" s="24" t="n"/>
+      <c r="G74" s="24" t="n"/>
+      <c r="H74" s="8" t="n"/>
+      <c r="I74" s="34" t="inlineStr">
+        <is>
+          <t>第6章第1節・第3節</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="34" t="inlineStr">
+        <is>
+          <t>令和11年度の65歳以上</t>
+        </is>
+      </c>
+      <c r="B75" s="35">
+        <f>ROUND(F36,0)</f>
+        <v/>
+      </c>
+      <c r="C75" s="24" t="n"/>
+      <c r="D75" s="24" t="n"/>
+      <c r="E75" s="24" t="n"/>
+      <c r="F75" s="24" t="n"/>
+      <c r="G75" s="24" t="n"/>
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="34" t="inlineStr">
+        <is>
+          <t>第6章第1節</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="34" t="inlineStr">
+        <is>
+          <t>令和11年度の認定率（％）</t>
+        </is>
+      </c>
+      <c r="B76" s="35">
+        <f>ROUND(G62,1)</f>
+        <v/>
+      </c>
+      <c r="C76" s="24" t="n"/>
+      <c r="D76" s="24" t="n"/>
+      <c r="E76" s="24" t="n"/>
+      <c r="F76" s="24" t="n"/>
+      <c r="G76" s="24" t="n"/>
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="34" t="inlineStr">
+        <is>
+          <t>第6章第1節</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="34" t="inlineStr">
+        <is>
+          <t>令和22年度の認定者数</t>
+        </is>
+      </c>
+      <c r="B77" s="35">
+        <f>ROUND(F65,0)</f>
+        <v/>
+      </c>
+      <c r="C77" s="24" t="n"/>
+      <c r="D77" s="24" t="n"/>
+      <c r="E77" s="24" t="n"/>
+      <c r="F77" s="24" t="n"/>
+      <c r="G77" s="24" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="34" t="inlineStr">
+        <is>
+          <t>第2章第8節</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>【8　検算　他シートの値との一致】</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>本シート</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>03シート</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr"/>
+      <c r="F80" s="3" t="inlineStr"/>
+      <c r="G80" s="3" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度の認定者数（基準）</t>
+        </is>
+      </c>
+      <c r="B81" s="9">
+        <f>ROUND(F58,0)</f>
+        <v/>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D81" s="9">
+        <f>B81-C81</f>
+        <v/>
+      </c>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="24" t="n"/>
+      <c r="G81" s="24" t="n"/>
+      <c r="H81" s="8" t="n"/>
+      <c r="I81" s="4">
+        <f>IF(ABS(D81)&lt;=1,"一致","要確認")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>令和11年度の認定者数</t>
+        </is>
+      </c>
+      <c r="B82" s="9">
+        <f>ROUND(F62,0)</f>
+        <v/>
+      </c>
+      <c r="C82" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D82" s="9">
+        <f>B82-C82</f>
+        <v/>
+      </c>
+      <c r="E82" s="5" t="inlineStr"/>
+      <c r="F82" s="24" t="n"/>
+      <c r="G82" s="24" t="n"/>
+      <c r="H82" s="8" t="n"/>
+      <c r="I82" s="4">
+        <f>IF(ABS(D82)&lt;=1,"一致","要確認")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>令和22年度の認定者数</t>
+        </is>
+      </c>
+      <c r="B83" s="9">
+        <f>ROUND(F65,0)</f>
+        <v/>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>2216</v>
+      </c>
+      <c r="D83" s="9">
+        <f>B83-C83</f>
+        <v/>
+      </c>
+      <c r="E83" s="5" t="inlineStr"/>
+      <c r="F83" s="24" t="n"/>
+      <c r="G83" s="24" t="n"/>
+      <c r="H83" s="8" t="n"/>
+      <c r="I83" s="4">
+        <f>IF(ABS(D83)&lt;=1,"一致","要確認")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>令和11年度の65歳以上</t>
+        </is>
+      </c>
+      <c r="B84" s="9">
+        <f>ROUND(F36,0)</f>
+        <v/>
+      </c>
+      <c r="C84" s="9" t="n">
+        <v>9072</v>
+      </c>
+      <c r="D84" s="9">
+        <f>B84-C84</f>
+        <v/>
+      </c>
+      <c r="E84" s="5" t="inlineStr"/>
+      <c r="F84" s="24" t="n"/>
+      <c r="G84" s="24" t="n"/>
+      <c r="H84" s="8" t="n"/>
+      <c r="I84" s="4">
+        <f>IF(ABS(D84)&lt;=1,"一致","要確認")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="104" customHeight="1">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>注1）本シートは、シナリオ2（トレンド継続）・人口補正なしの状態で他シートと一致するように作っている。【8】の判定欄がすべて「一致」であることを確認したうえで、入力欄を変更していただきたい。注2）人口補正を適用する場合は【1】の「人口補正の適用」を1にする。補正係数は【2】のE列で変更できる。初期値は1.000（補正なしと同じ）としているため、適用する場合は65〜74歳に1.0377、75〜84歳及び85歳以上に0.9927を入力する（人口推計の補正 04シートによる）。注3）本シートで変更できるのは第1段階（人口と認定者数）までである。サービス見込量（第2段階）及び給付費・保険料（第3段階）への波及は、【7】の転記値を各成果品に入力して再計算する。注4）他のシート（00〜07）は本シートの計算結果を書き出した転記表である。入力欄を変更しても他のシートは自動では変わらない。変更を成果品に反映する場合は受託者にご連絡いただきたい。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B74:H74"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A86:I86"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B72:H72"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="B71:H71"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B77:H77"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B73:H73"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="F51:H51"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/第10期計画_将来推計_人口と認定者数.xlsx
+++ b/output/第10期計画_将来推計_人口と認定者数.xlsx
@@ -3701,7 +3701,7 @@
     <row r="19" ht="104" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>注1）シナリオの決定（方針No.2）は、第6章第1節の認定者数の見込み、第2節の見込量、第3節の給付費、第6節の保険料に順に波及する。令和8年12月の工程（計画素案の確定版）に間に合わせるには令和8年10月中の決定が必要である。注2）本表は認定率のみをシナリオとしている。施策効果の見込み方（方針No.3）は別の論点である。施策効果を見込む場合は、②のトレンドに上乗せするのではなく、どの施策がどの階級の認定率を何ポイント下げるかを示す必要がある。注3）第10期の重点は、認定率の分析の結果、重度化防止から介護予防（軽度認定の抑制）へ移る。中重度（要介護3〜5）の調整済み認定率は5.4％から4.7％へ低下が続く一方、軽度（要支援1〜要介護2）は令和5年11.7％を底に令和7年12.0％へ上昇に転じている。</t>
+          <t>注1）シナリオの決定（方針No.2）は、第6章第1節の認定者数の見込み、第2節の見込量、第3節の給付費、第6節の保険料に順に波及する。令和8年12月の工程（計画素案の確定版）に間に合わせるには令和8年10月中の決定が必要である。注2）本表は認定率のみをシナリオとしている。施策効果の見込み方（方針No.3）は別の論点である。施策効果を見込む場合は、②のトレンドに上乗せするのではなく、どの施策がどの階級の認定率を何ポイント下げるかを示す必要がある。注3）第10期の重点は、認定率の分析の結果、重度化防止を継続しつつフレイル予防と早期支援の強化へ広がる。中重度（要介護3〜5）の調整済み認定率は5.4％から4.7％へ低下が続く一方、軽度（要支援1〜要介護2）は令和5年11.7％を底に令和7年12.0％へ上昇に転じている。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_将来推計_人口と認定者数.xlsx
+++ b/output/第10期計画_将来推計_人口と認定者数.xlsx
@@ -718,12 +718,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>社人研推計（令和5年推計・令和2年国勢調査基準）による。第10期期間中、総人口は▲3.3％、65歳以上人口は▲0.1％。</t>
+          <t>社人研推計（令和5年推計・令和2年国勢調査基準）を参考として掲げる。第10期期間中、総人口は▲3.3％、65歳以上人口は▲0.1％。推計に用いる伸び率は02シートのとおり住民基本台帳による。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>方針No.1 確認待ち</t>
+          <t>令和8年8月31日のご指示</t>
         </is>
       </c>
     </row>
@@ -740,12 +740,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>階級別人口＝令和7年度の実績人口×社人研推計の階級別の伸び率。</t>
+          <t>階級別人口＝令和7年度の実績人口×住民基本台帳の実績趨勢による階級別の伸び率。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>令和11年度の65歳以上は9,072人（令和7年度9,090人）。85歳以上は1,990人から2,072人へ4.1％増える。</t>
+          <t>令和11年度の65歳以上は9,213人（令和7年度9,090人）。85歳以上は1,990人から2,152人へ8.1％増える。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>令和11年度の認定者数は、①現状固定2,044人、②トレンド継続2,004人、③令和元年水準2,112人。</t>
+          <t>令和11年度の認定者数は、①現状固定2,108人、②トレンド継続2,067人、③令和元年水準2,178人。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>②トレンド継続を推奨する。第10期の3年間の認定者数の合計は①6,087人・②5,999人・③6,240人で、最大と最小の差は241人（4.0％）。</t>
+          <t>②トレンド継続を推奨する。第10期の3年間の認定者数の合計は①6,229人・②6,138人・③6,385人で、最大と最小の差は247人（4.0％）。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1161,14 +1161,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>人口推計の基礎（受託者の案：社人研推計をそのまま用いる）</t>
+          <t>人口推計の基礎（総合戦略上の人口による）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和8年7月30日、人口推計の基礎について社人研推計（見える化システムの初期値）をそのまま用いることを受託者の案とする。見える化A系列の値をそのまま前提とする。</t>
+          <t>令和8年8月31日のご指示により、人口推計の基礎は社人研推計ではなく総合戦略上の人口とする。総合戦略は総人口の目標のみを持つため、年齢階級別の伸び率は住民基本台帳の実績趨勢による（02シート）。本シートは、参考として見える化A系列（社人研）の値を掲げる。</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>試算の前提（受託者の案）</t>
+          <t>採用する基礎（令和8年8月31日のご指示）</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>第10期の人口推計の基礎は、国立社会保障・人口問題研究所「日本の地域別将来推計人口」（令和5年推計・令和2年国勢調査基準）をそのまま用いる。見える化システムの初期値である。</t>
+          <t>第10期の人口推計の基礎は、社人研推計ではなく総合戦略上の人口とする。総人口は3町の地方創生総合戦略（人口ビジョン）の目標人口を、年齢階級別の伸び率は住民基本台帳の実績趨勢（平成31年〜令和7年の年平均変化率）を用いる。</t>
         </is>
       </c>
       <c r="C18" s="24" t="n"/>
@@ -1597,12 +1597,12 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>この前提の位置付け</t>
+          <t>階級別を住民基本台帳によることの理由</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>受託者の案であり、決定した事項ではない。仕様書の定めにより、業務の各工程においてその都度発注者の意向を確認する。本シートの試算は、作業を止めないためにこの案を仮に置いたものである。</t>
+          <t>総合戦略が持つのは総人口の目標のみであり、65歳以上・75歳以上の内訳を持たない。認定者数の推計は階級別人口を要するため、階級別の伸び率は住民基本台帳の実績趨勢による。詳細は「人口推計の基礎の変更_総合戦略ベース」による。</t>
         </is>
       </c>
       <c r="C19" s="24" t="n"/>
@@ -1616,12 +1616,12 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>意向を確認する時期</t>
+          <t>この基礎を採ることの根拠</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>キックオフ会議（ヒアリングシート項目6-1）。他の系列によるとの意向がある場合は、02〜06シートを再計算する。</t>
+          <t>「自然体推計の計算過程確認シートのガイド」は、保険者が保有する総合計画等による推計人口を用いることを基本とし、これを用意できない場合に社人研推計を利用することとしている。総合戦略上の人口を用いることは、このガイドの原則に沿う。</t>
         </is>
       </c>
       <c r="C20" s="24" t="n"/>
@@ -1635,12 +1635,12 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>仮に置かなかった選択肢</t>
+          <t>令和12年度以降の扱い</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>②3町の総合計画等による推計人口への差替え、③社人研推計を基本とし東川町のみ感度分析として別途示す。</t>
+          <t>総合戦略は令和11年度までしか目標を持たない。中長期推計（令和22年度・令和32年度）は社人研推計によらざるを得ないため、第10期の3年間と中長期とで基礎が異なることを計画本文に明記する。</t>
         </is>
       </c>
       <c r="C21" s="24" t="n"/>
@@ -1654,12 +1654,12 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>この前提を記録する理由</t>
+          <t>従前の案の扱い</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>「自然体推計の計算過程確認シートのガイド」は、保険者が保有する総合計画等による推計人口を用いることを基本とし、これを用意できない場合に社人研推計を利用することとしている。社人研推計を用いる場合はその理由を記録に残す必要がある。</t>
+          <t>令和8年7月30日に受託者が仮に置いた案（社人研推計をそのまま用いる）は、本シートの参考表及び「人口推計の補正_65歳以上75歳以上の突合」に案A・案Bとして残す。対比の記録として保存する。</t>
         </is>
       </c>
       <c r="C22" s="24" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>意向の確認を経て基礎が定まった段階で、第2章第1節に、人口推計の基礎、第9期計画（住民基本台帳・コーホート変化率法）の数値と一致しないこと、及びその理由を記載する。現時点の計画素案では当該箇所に［要協議］を付している。</t>
+          <t>第2章第1節に、人口推計の基礎、第9期計画（住民基本台帳・コーホート変化率法）の数値と一致しないこと、及びその理由を記載する。</t>
         </is>
       </c>
       <c r="C23" s="24" t="n"/>
@@ -1692,12 +1692,12 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>なお残る作業</t>
+          <t>なお確定を要すること</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳実績（資料No.9）を受領した際は、社人研推計との乖離を確認し、社人研推計との乖離を確認し、乖離が大きい場合は第2章に注記する。基礎そのものを変更するかどうかは発注者の意向による。</t>
+          <t>美瑛町の総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることから、総人口の目標値を3町一律には用いられない。確定を要する事項は「人口推計の基礎の変更_総合戦略ベース」06シートによる。</t>
         </is>
       </c>
       <c r="C24" s="24" t="n"/>
@@ -1711,7 +1711,7 @@
     <row r="26" ht="104" customHeight="1">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>注1）本シートの人口は見える化A系列のとおりである。第10期の推計に用いる各年度の値は、5年ごとの推計点（令和7年・令和12年）の線形補間である。注2）総人口は第10期の3年間で3.3％減少するが、65歳以上人口は0.1％減にとどまる。高齢化率の上昇（34.4％→35.6％）は分母の減少によるものであり、高齢者が増えるためではない。注3）第10期基本指針案は2040年度を含む中長期推計を求めている。令和22年度（2040年）及び令和32年度（2050年）を掲載する。</t>
+          <t>注1）本シートの人口は見える化A系列（社人研）のとおりであり、参考である。推計に用いる階級別人口は02シートによる。第10期の推計に用いる各年度の値は、5年ごとの推計点（令和7年・令和12年）の線形補間である。注2）総人口は第10期の3年間で3.3％減少するが、65歳以上人口は0.1％減にとどまる。高齢化率の上昇（34.4％→35.6％）は分母の減少によるものであり、高齢者が増えるためではない。注3）第10期基本指針案は2040年度を含む中長期推計を求めている。令和22年度（2040年）及び令和32年度（2050年）を掲載する。</t>
         </is>
       </c>
     </row>
@@ -1756,14 +1756,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>推計上の階級別人口（実績人口×社人研推計の伸び率）</t>
+          <t>推計上の階級別人口（実績人口×住民基本台帳の実績趨勢）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和7年度の実績人口（見える化B4系列・令和8年3月末）に、社人研推計の階級別の伸び率（見える化A4）を乗じて求める。基準年度の水準を実績に合わせることで、推計の出発点が実績と一致する。</t>
+          <t>令和7年度の実績人口（見える化B4系列・令和8年3月末）に、住民基本台帳の階級別の実績趨勢（平成31年〜令和7年の年平均変化率）を乗じて求める。基準年度の水準を実績に合わせることで、推計の出発点が実績と一致する。令和12年度以降は、令和11年度を起点に社人研推計の伸び率で接続する（総合戦略が令和11年度までしか目標を持たないため）。</t>
         </is>
       </c>
     </row>
@@ -1878,30 +1878,30 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>3551</v>
+        <v>3542</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>3524</v>
+        <v>3546</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>2011</v>
+        <v>2030</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>9086</v>
+        <v>9117</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>0.9862</t>
+          <t>0.9838</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>1.0071</t>
+          <t>1.0133</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>1.0106</t>
+          <t>1.0197</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr"/>
@@ -1918,30 +1918,30 @@
         </is>
       </c>
       <c r="C7" s="19" t="n">
-        <v>3501</v>
+        <v>3484</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>3548</v>
+        <v>3593</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>2032</v>
+        <v>2070</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>9080</v>
+        <v>9147</v>
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>0.9724</t>
+          <t>0.9678</t>
         </is>
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
-          <t>1.0139</t>
+          <t>1.0267</t>
         </is>
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
-          <t>1.0208</t>
+          <t>1.0399</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr"/>
@@ -1958,30 +1958,30 @@
         </is>
       </c>
       <c r="C8" s="19" t="n">
-        <v>3452</v>
+        <v>3428</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>3574</v>
+        <v>3641</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>2052</v>
+        <v>2111</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>9078</v>
+        <v>9179</v>
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
-          <t>0.9589</t>
+          <t>0.9521</t>
         </is>
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>1.0212</t>
+          <t>1.0404</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>1.0309</t>
+          <t>1.0604</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr"/>
@@ -1998,35 +1998,35 @@
         </is>
       </c>
       <c r="C9" s="19" t="n">
-        <v>3403</v>
+        <v>3372</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>3597</v>
+        <v>3689</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>2072</v>
+        <v>2152</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>9072</v>
+        <v>9213</v>
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>0.9451</t>
+          <t>0.9366</t>
         </is>
       </c>
       <c r="H9" s="19" t="inlineStr">
         <is>
-          <t>1.0280</t>
+          <t>1.0542</t>
         </is>
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
-          <t>1.0411</t>
+          <t>1.0814</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
         <is>
-          <t>第10期の最終年度。85歳以上が82人増える一方、65〜74歳は197人減る</t>
+          <t>第10期の最終年度。85歳以上が+161人、75〜84歳が+189人、65〜74歳が-228人</t>
         </is>
       </c>
     </row>
@@ -2042,33 +2042,37 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>3353</v>
+        <v>3323</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>3622</v>
+        <v>3714</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2093</v>
+        <v>2174</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>9068</v>
+        <v>9211</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>0.9313</t>
+          <t>0.9229</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1.0351</t>
+          <t>1.0615</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>1.0517</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
+          <t>1.0924</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>令和12年度以降は社人研推計の伸び率で接続する</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="21" t="inlineStr">
@@ -2082,35 +2086,35 @@
         </is>
       </c>
       <c r="C11" s="22" t="n">
-        <v>3564</v>
+        <v>3532</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>3089</v>
+        <v>3168</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>2455</v>
+        <v>2550</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>9108</v>
+        <v>9250</v>
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>0.9898</t>
+          <t>0.9809</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
         <is>
-          <t>0.8829</t>
+          <t>0.9053</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
         <is>
-          <t>1.2335</t>
+          <t>1.2812</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>75〜84歳が3,089人へ減少。85歳以上は2,455人へ増加</t>
+          <t>75〜84歳が3,168人、85歳以上が2,550人</t>
         </is>
       </c>
     </row>
@@ -2126,37 +2130,33 @@
         </is>
       </c>
       <c r="C12" s="22" t="n">
-        <v>3862</v>
+        <v>3827</v>
       </c>
       <c r="D12" s="22" t="n">
-        <v>2909</v>
+        <v>2983</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>2581</v>
+        <v>2681</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>9352</v>
+        <v>9491</v>
       </c>
       <c r="G12" s="22" t="inlineStr">
         <is>
-          <t>1.0726</t>
+          <t>1.0630</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
         <is>
-          <t>0.8314</t>
+          <t>0.8525</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
-          <t>1.2967</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>85歳以上が2,581人でピーク。65〜74歳も3,862人へ回復する</t>
-        </is>
-      </c>
+          <t>1.3469</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="21" t="inlineStr">
@@ -2170,30 +2170,30 @@
         </is>
       </c>
       <c r="C13" s="22" t="n">
-        <v>3754</v>
+        <v>3720</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>3119</v>
+        <v>3199</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>2384</v>
+        <v>2477</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>9257</v>
+        <v>9395</v>
       </c>
       <c r="G13" s="22" t="inlineStr">
         <is>
-          <t>1.0425</t>
+          <t>1.0332</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
         <is>
-          <t>0.8913</t>
+          <t>0.9140</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t>1.1980</t>
+          <t>1.2443</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr"/>
@@ -2210,30 +2210,30 @@
         </is>
       </c>
       <c r="C14" s="22" t="n">
-        <v>3242</v>
+        <v>3213</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>3410</v>
+        <v>3497</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>2327</v>
+        <v>2417</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>8979</v>
+        <v>9127</v>
       </c>
       <c r="G14" s="22" t="inlineStr">
         <is>
-          <t>0.9003</t>
+          <t>0.8923</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
         <is>
-          <t>0.9745</t>
+          <t>0.9994</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
-          <t>1.1694</t>
+          <t>1.2146</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr"/>
@@ -2295,17 +2295,17 @@
         <v>3600</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>3501</v>
+        <v>3484</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>3452</v>
+        <v>3428</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>3403</v>
+        <v>3372</v>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>-198人（-5.5％）</t>
+          <t>-228人（-6.3％）</t>
         </is>
       </c>
       <c r="G18" s="24" t="n"/>
@@ -2327,17 +2327,17 @@
         <v>3499</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>3548</v>
+        <v>3593</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>3574</v>
+        <v>3641</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>3597</v>
+        <v>3689</v>
       </c>
       <c r="F19" s="27" t="inlineStr">
         <is>
-          <t>+98人（+2.8％）</t>
+          <t>+190人（+5.4％）</t>
         </is>
       </c>
       <c r="G19" s="24" t="n"/>
@@ -2359,17 +2359,17 @@
         <v>1990</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>2032</v>
+        <v>2070</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>2052</v>
+        <v>2111</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2072</v>
+        <v>2152</v>
       </c>
       <c r="F20" s="27" t="inlineStr">
         <is>
-          <t>+82人（+4.1％）</t>
+          <t>+162人（+8.1％）</t>
         </is>
       </c>
       <c r="G20" s="24" t="n"/>
@@ -2391,17 +2391,17 @@
         <v>9090</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>9080</v>
+        <v>9147</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>9078</v>
+        <v>9179</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>9072</v>
+        <v>9213</v>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>-18人（-0.2％）</t>
+          <t>+123人（+1.4％）</t>
         </is>
       </c>
       <c r="G21" s="24" t="n"/>
@@ -2416,7 +2416,7 @@
     <row r="23" ht="104" customHeight="1">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>注1）本表の人口は「第1号被保険者数」ではなく「認定率の分母となる65歳以上人口」である。第1号被保険者数は住所地特例等により若干異なる。保険料算定に用いる被保険者数は第3段階で別途整理する。注2）伸び率は見える化A4（国勢調査・社人研推計）による。A4の各年の値は5年ごとの推計点の線形補間であるため、伸び率も区間内では一定である。注3）65歳以上の合計は第10期の3年間でほぼ変わらないが、85歳以上が82人増え65〜74歳が197人減る。階級別の認定率が大きく異なるため、この構成の変化だけで合計認定率は上昇する。</t>
+          <t>注1）本表の人口は「第1号被保険者数」ではなく「認定率の分母となる65歳以上人口」である。第1号被保険者数は住所地特例等により若干異なる。保険料算定に用いる被保険者数は第3段階で別途整理する。注2）伸び率は住民基本台帳（平成31年〜令和7年の6年）の階級別の年平均変化率による（65〜74歳-1.624％・75〜84歳+1.328％・85歳以上+1.975％）。令和8年8月31日の発注者のご指示により、社人研推計を伸び率の基礎とすることをやめた。令和12年度以降は総合戦略に目標がないため、令和11年度を起点に社人研推計の伸び率で接続している。注3）65歳以上の合計は第10期の3年間で+123人となり、85歳以上が+162人増え65〜74歳が-228人減る。階級別の認定率が大きく異なるため、この構成の変化だけで合計認定率は上昇する。</t>
         </is>
       </c>
     </row>
@@ -2630,27 +2630,27 @@
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>1999</v>
+        <v>2014</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
+          <t>22.1％</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
           <t>22.0％</t>
         </is>
       </c>
-      <c r="H6" s="9" t="n">
-        <v>1990</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>21.9％</t>
-        </is>
-      </c>
       <c r="J6" s="9" t="n">
-        <v>2016</v>
+        <v>2031</v>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>22.2％</t>
+          <t>22.3％</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -2691,32 +2691,32 @@
         </is>
       </c>
       <c r="F7" s="19" t="n">
-        <v>2014</v>
+        <v>2045</v>
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>22.2％</t>
+          <t>22.4％</t>
         </is>
       </c>
       <c r="H7" s="19" t="n">
-        <v>1995</v>
+        <v>2025</v>
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
-          <t>22.0％</t>
+          <t>22.1％</t>
         </is>
       </c>
       <c r="J7" s="19" t="n">
-        <v>2048</v>
+        <v>2079</v>
       </c>
       <c r="K7" s="19" t="inlineStr">
         <is>
-          <t>22.5％</t>
+          <t>22.7％</t>
         </is>
       </c>
       <c r="L7" s="19" t="inlineStr">
         <is>
-          <t>-19人</t>
+          <t>-20人</t>
         </is>
       </c>
       <c r="M7" s="19" t="inlineStr">
@@ -2752,37 +2752,37 @@
         </is>
       </c>
       <c r="F8" s="19" t="n">
-        <v>2029</v>
+        <v>2076</v>
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
-          <t>22.4％</t>
+          <t>22.6％</t>
         </is>
       </c>
       <c r="H8" s="19" t="n">
-        <v>2000</v>
+        <v>2046</v>
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>22.0％</t>
+          <t>22.3％</t>
         </is>
       </c>
       <c r="J8" s="19" t="n">
-        <v>2080</v>
+        <v>2128</v>
       </c>
       <c r="K8" s="19" t="inlineStr">
         <is>
-          <t>22.9％</t>
+          <t>23.2％</t>
         </is>
       </c>
       <c r="L8" s="19" t="inlineStr">
         <is>
-          <t>-29人</t>
+          <t>-30人</t>
         </is>
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
-          <t>+51人</t>
+          <t>+52人</t>
         </is>
       </c>
     </row>
@@ -2813,37 +2813,37 @@
         </is>
       </c>
       <c r="F9" s="19" t="n">
-        <v>2044</v>
+        <v>2108</v>
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>22.5％</t>
+          <t>22.9％</t>
         </is>
       </c>
       <c r="H9" s="19" t="n">
-        <v>2004</v>
+        <v>2067</v>
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
-          <t>22.1％</t>
+          <t>22.4％</t>
         </is>
       </c>
       <c r="J9" s="19" t="n">
-        <v>2112</v>
+        <v>2178</v>
       </c>
       <c r="K9" s="19" t="inlineStr">
         <is>
-          <t>23.3％</t>
+          <t>23.6％</t>
         </is>
       </c>
       <c r="L9" s="19" t="inlineStr">
         <is>
-          <t>-39人</t>
+          <t>-40人</t>
         </is>
       </c>
       <c r="M9" s="19" t="inlineStr">
         <is>
-          <t>+68人</t>
+          <t>+71人</t>
         </is>
       </c>
     </row>
@@ -2874,37 +2874,37 @@
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>2059</v>
+        <v>2124</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>22.7％</t>
+          <t>23.1％</t>
         </is>
       </c>
       <c r="H10" s="9" t="n">
-        <v>2019</v>
+        <v>2083</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>22.3％</t>
+          <t>22.6％</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2128</v>
+        <v>2195</v>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>23.5％</t>
+          <t>23.8％</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>-39人</t>
+          <t>-41人</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>+69人</t>
+          <t>+71人</t>
         </is>
       </c>
     </row>
@@ -2935,37 +2935,37 @@
         </is>
       </c>
       <c r="F11" s="22" t="n">
-        <v>2197</v>
+        <v>2268</v>
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
+          <t>24.5％</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="n">
+        <v>2228</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
           <t>24.1％</t>
         </is>
       </c>
-      <c r="H11" s="22" t="n">
-        <v>2158</v>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>23.7％</t>
-        </is>
-      </c>
       <c r="J11" s="22" t="n">
-        <v>2265</v>
+        <v>2338</v>
       </c>
       <c r="K11" s="22" t="inlineStr">
         <is>
-          <t>24.9％</t>
+          <t>25.3％</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
         <is>
-          <t>-39人</t>
+          <t>-40人</t>
         </is>
       </c>
       <c r="M11" s="22" t="inlineStr">
         <is>
-          <t>+68人</t>
+          <t>+70人</t>
         </is>
       </c>
     </row>
@@ -2996,37 +2996,37 @@
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>2255</v>
+        <v>2328</v>
       </c>
       <c r="G12" s="22" t="inlineStr">
         <is>
+          <t>24.5％</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="n">
+        <v>2288</v>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
           <t>24.1％</t>
         </is>
       </c>
-      <c r="H12" s="22" t="n">
-        <v>2216</v>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
-        <is>
-          <t>23.7％</t>
-        </is>
-      </c>
       <c r="J12" s="22" t="n">
-        <v>2323</v>
+        <v>2398</v>
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t>24.8％</t>
+          <t>25.3％</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr">
         <is>
-          <t>-39人</t>
+          <t>-40人</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
         <is>
-          <t>+68人</t>
+          <t>+70人</t>
         </is>
       </c>
     </row>
@@ -3057,37 +3057,37 @@
         </is>
       </c>
       <c r="F13" s="22" t="n">
-        <v>2166</v>
+        <v>2236</v>
       </c>
       <c r="G13" s="22" t="inlineStr">
         <is>
+          <t>23.8％</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="n">
+        <v>2196</v>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
           <t>23.4％</t>
         </is>
       </c>
-      <c r="H13" s="22" t="n">
-        <v>2128</v>
-      </c>
-      <c r="I13" s="22" t="inlineStr">
-        <is>
-          <t>23.0％</t>
-        </is>
-      </c>
       <c r="J13" s="22" t="n">
-        <v>2234</v>
+        <v>2305</v>
       </c>
       <c r="K13" s="22" t="inlineStr">
         <is>
-          <t>24.1％</t>
+          <t>24.5％</t>
         </is>
       </c>
       <c r="L13" s="22" t="inlineStr">
         <is>
-          <t>-38人</t>
+          <t>-40人</t>
         </is>
       </c>
       <c r="M13" s="22" t="inlineStr">
         <is>
-          <t>+67人</t>
+          <t>+69人</t>
         </is>
       </c>
     </row>
@@ -3118,37 +3118,37 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>2162</v>
+        <v>2231</v>
       </c>
       <c r="G14" s="22" t="inlineStr">
         <is>
-          <t>24.1％</t>
+          <t>24.4％</t>
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>2122</v>
+        <v>2190</v>
       </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
-          <t>23.6％</t>
+          <t>24.0％</t>
         </is>
       </c>
       <c r="J14" s="22" t="n">
-        <v>2232</v>
+        <v>2303</v>
       </c>
       <c r="K14" s="22" t="inlineStr">
         <is>
-          <t>24.9％</t>
+          <t>25.2％</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr">
         <is>
-          <t>-40人</t>
+          <t>-41人</t>
         </is>
       </c>
       <c r="M14" s="22" t="inlineStr">
         <is>
-          <t>+70人</t>
+          <t>+72人</t>
         </is>
       </c>
     </row>
@@ -3211,10 +3211,10 @@
       <c r="F18" s="24" t="n"/>
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="9" t="n">
-        <v>2044</v>
+        <v>2108</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>2255</v>
+        <v>2328</v>
       </c>
       <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="24" t="n"/>
@@ -3242,10 +3242,10 @@
       <c r="F19" s="24" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="9" t="n">
-        <v>2004</v>
+        <v>2067</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>2216</v>
+        <v>2288</v>
       </c>
       <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="24" t="n"/>
@@ -3273,10 +3273,10 @@
       <c r="F20" s="24" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="9" t="n">
-        <v>2112</v>
+        <v>2178</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>2323</v>
+        <v>2398</v>
       </c>
       <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="24" t="n"/>
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>2014</v>
+        <v>2045</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2029</v>
+        <v>2076</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2044</v>
+        <v>2108</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>6087</v>
+        <v>6229</v>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="24" t="n"/>
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>1995</v>
+        <v>2025</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>2000</v>
+        <v>2046</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>2004</v>
+        <v>2067</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>5999</v>
+        <v>6138</v>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="24" t="n"/>
@@ -3391,7 +3391,7 @@
       <c r="L25" s="8" t="n"/>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>-88人（-1.4％）</t>
+          <t>-91人（-1.5％）</t>
         </is>
       </c>
     </row>
@@ -3402,16 +3402,16 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>2048</v>
+        <v>2079</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2080</v>
+        <v>2128</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>2112</v>
+        <v>2178</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>6240</v>
+        <v>6385</v>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="24" t="n"/>
@@ -3422,14 +3422,14 @@
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>+153人（+2.5％）</t>
+          <t>+156人（+2.5％）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="104" customHeight="1">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>注1）第10期の3年間の認定者数の合計は、①現状固定6087人、②トレンド継続5999人、③令和元年水準6240人である。最大と最小の差は241人（4.0％）であり、給付費に換算すると3年間で概ね1億円台の差となる見込みである（受給者単価による。第3段階で算定する）。注2）いずれのシナリオでも認定者数は増える。第10期期間中に65歳以上人口はほぼ変わらないが、85歳以上が4.1％増えるためである。認定率が令和8年の水準で固定されても認定者数は3.0％増える。注3）合計認定率（認定者数÷65歳以上人口）は令和7年度21.8％から令和11年度に①22.5％・②22.1％・③23.3％となる。年齢構成の変化により、認定率が改善しても合計率は上昇する。</t>
+          <t>注1）第10期の3年間の認定者数の合計は、①現状固定6229人、②トレンド継続6138人、③令和元年水準6385人である。最大と最小の差は247人（4.0％）であり、給付費に換算すると3年間で概ね1億円台の差となる見込みである（受給者単価による。第3段階で算定する）。注2）いずれのシナリオでも認定者数は増える。第10期期間中に65歳以上人口はほぼ変わらないが、85歳以上が4.1％増えるためである。認定率が令和8年の水準で固定されても認定者数は3.0％増える。注3）合計認定率（認定者数÷65歳以上人口）は令和7年度21.8％から令和11年度に①22.5％・②22.1％・③23.3％となる。年齢構成の変化により、認定率が改善しても合計率は上昇する。</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>2044</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="6" ht="120" customHeight="1">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>2004</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="7" ht="120" customHeight="1">
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="F7" s="9" t="n">
-        <v>2112</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>A系列を水準としてそのまま用いた場合、令和11年度の認定者数は2164人となり、本推計（2044人）を5.9％上回る。</t>
+          <t>A系列を水準としてそのまま用いた場合、令和11年度の認定者数は2164人となり、本推計（2108人）を2.7％上回る。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -4289,14 +4289,14 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>2044</v>
+        <v>2108</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>2164</v>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>+120人（+5.9％）</t>
+          <t>+56人（+2.7％）</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -4312,14 +4312,14 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>2255</v>
+        <v>2328</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>2402</v>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>+147人（+6.5％）</t>
+          <t>+74人（+3.2％）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -6986,7 +6986,7 @@
         <v/>
       </c>
       <c r="C82" s="9" t="n">
-        <v>2004</v>
+        <v>2067</v>
       </c>
       <c r="D82" s="9">
         <f>B82-C82</f>
@@ -7012,7 +7012,7 @@
         <v/>
       </c>
       <c r="C83" s="9" t="n">
-        <v>2216</v>
+        <v>2288</v>
       </c>
       <c r="D83" s="9">
         <f>B83-C83</f>
@@ -7038,7 +7038,7 @@
         <v/>
       </c>
       <c r="C84" s="9" t="n">
-        <v>9072</v>
+        <v>9213</v>
       </c>
       <c r="D84" s="9">
         <f>B84-C84</f>
